--- a/technology_surveys/018_functionalities_selection_survey--technology_surveys.xlsx
+++ b/technology_surveys/018_functionalities_selection_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -767,7 +767,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How satisfied are you with this product?</t>
+          <t>Main Page Satisfaction</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Contact Phone</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Main Page Future Ideas Comments</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>next_release_ideas</t>
+          <t>next_release_ideas_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>What features would you like to see prioritized in the next release?</t>
+          <t>Next Release Ideas 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>next_release_comments</t>
+          <t>next_release_comments_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Next Release Comments 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Improvement ideas</t>
+          <t>Email Ideas</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1122,8 +1122,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option':_'feature_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option': 'Feature 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option':_'feature_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option': 'Feature 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option':_'feature_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option': 'Feature 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option':_'very_important'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option': 'Very important'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'somewhat_important'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 'Somewhat important'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_'not_very_important'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': 'Not very important'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_'very_satisfied'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': 'Very satisfied'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_'somewhat_satisfied'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': 'Somewhat satisfied'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_'not_satisfied'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': 'Not satisfied'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_'feature_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': 'Feature 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_'feature_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': 'Feature 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option':_'feature_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option': 'Feature 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option':_'very_satisfied'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option': 'Very satisfied'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option':_'somewhat_satisfied'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option': 'Somewhat satisfied'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option':_'not_satisfied'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option': 'Not satisfied'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option':_'very_happy'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option': 'Very happy'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option':_'somewhat_happy'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option': 'Somewhat happy'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option':_'not_happy'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option': 'Not happy'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option':_'very_happy'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option': 'Very happy'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option':_'somewhat_happy'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option': 'Somewhat happy'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option':_'not_happy'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option': 'Not happy'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option':_'feature_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option': 'Feature 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option':_'feature_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option': 'Feature 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option':_'feature_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option': 'Feature 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option':_'very_satisfied'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option': 'Very satisfied'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'option':_'somewhat_satisfied'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'option': 'Somewhat satisfied'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1593,63 +1593,63 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'option':_'not_satisfied'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'option': 'Not satisfied'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>next_release_ideas_choices</t>
+          <t>next_release_ideas_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'option':_'feature_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'option': 'Feature 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>next_release_ideas_choices</t>
+          <t>next_release_ideas_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'option':_'feature_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'option': 'Feature 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>next_release_ideas_choices</t>
+          <t>next_release_ideas_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'option':_'feature_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'option': 'Feature 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
